--- a/dataset/v2/hse_progress.xlsx
+++ b/dataset/v2/hse_progress.xlsx
@@ -569,12 +569,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Manifold</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>26/Nov/2026</t>
+          <t>2026-11-26</t>
         </is>
       </c>
     </row>
@@ -606,7 +611,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -616,7 +621,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/Dec/2026</t>
         </is>
       </c>
     </row>
@@ -646,19 +651,14 @@
           <t>HSE</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Manifold</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>03/Mar/2027</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12/03/2027</t>
+          <t>12/Mar/2027</t>
         </is>
       </c>
     </row>
@@ -688,6 +688,11 @@
           <t>HSE</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Manifold</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>04/01/2027</t>
@@ -727,12 +732,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Substation</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2027-02-04</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manifold</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>27/02/2027</t>
+          <t>27/Feb/2027</t>
         </is>
       </c>
     </row>
@@ -811,17 +811,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>31/Oct/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -851,11 +851,6 @@
           <t>HSE</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>09/11/2026</t>
@@ -863,7 +858,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>2026-11-09</t>
         </is>
       </c>
     </row>
@@ -895,12 +890,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>21/Sep/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -937,7 +932,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -990,12 +985,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>01/Mar/2027</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>05/03/2027</t>
+          <t>05/Mar/2027</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1031,11 +1026,6 @@
           <t>HSE</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>12/11/2026</t>
@@ -1076,17 +1066,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>06/Nov/2026</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>09/Nov/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1124,12 +1109,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11/11/2026</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1166,7 +1151,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1176,7 +1161,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>20/Mar/2026</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1219,12 +1204,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>25/Mar/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>26/Mar/2026</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1262,17 +1247,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>16/Mar/2026</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1310,7 +1295,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1358,17 +1343,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manifold</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1404,14 +1384,19 @@
           <t>HSE</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Substation</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1454,12 +1439,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23/12/2026</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>27/12/2026</t>
         </is>
       </c>
       <c r="I25" t="n">
